--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="104">
   <si>
     <t>FirstName</t>
   </si>
@@ -287,6 +287,66 @@
   </si>
   <si>
     <t>vikram1780725274948</t>
+  </si>
+  <si>
+    <t>surya1780743100276</t>
+  </si>
+  <si>
+    <t>arun1780743103686</t>
+  </si>
+  <si>
+    <t>priya1780743107074</t>
+  </si>
+  <si>
+    <t>rahul1780743110366</t>
+  </si>
+  <si>
+    <t>divya1780743113974</t>
+  </si>
+  <si>
+    <t>karthik1780743117322</t>
+  </si>
+  <si>
+    <t>meena1780743121643</t>
+  </si>
+  <si>
+    <t>sanjay1780743125435</t>
+  </si>
+  <si>
+    <t>anitha1780743129303</t>
+  </si>
+  <si>
+    <t>vikram1780743133676</t>
+  </si>
+  <si>
+    <t>surya1780744850810</t>
+  </si>
+  <si>
+    <t>arun1780744855452</t>
+  </si>
+  <si>
+    <t>priya1780744860025</t>
+  </si>
+  <si>
+    <t>rahul1780744864019</t>
+  </si>
+  <si>
+    <t>divya1780744868072</t>
+  </si>
+  <si>
+    <t>karthik1780744873319</t>
+  </si>
+  <si>
+    <t>meena1780744877513</t>
+  </si>
+  <si>
+    <t>sanjay1780744881493</t>
+  </si>
+  <si>
+    <t>anitha1780744886133</t>
+  </si>
+  <si>
+    <t>vikram1780744890699</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1103,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>53</v>
@@ -1054,7 +1114,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>53</v>
@@ -1065,7 +1125,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>53</v>
@@ -1076,7 +1136,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>53</v>
@@ -1087,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>53</v>
@@ -1098,7 +1158,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>53</v>
@@ -1109,7 +1169,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>53</v>
@@ -1120,7 +1180,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>53</v>
@@ -1131,7 +1191,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>53</v>
@@ -1142,7 +1202,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>53</v>

--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="114">
   <si>
     <t>FirstName</t>
   </si>
@@ -347,6 +347,36 @@
   </si>
   <si>
     <t>vikram1780744890699</t>
+  </si>
+  <si>
+    <t>surya1780900788437</t>
+  </si>
+  <si>
+    <t>arun1780900792094</t>
+  </si>
+  <si>
+    <t>priya1780900795925</t>
+  </si>
+  <si>
+    <t>rahul1780900800143</t>
+  </si>
+  <si>
+    <t>divya1780900804784</t>
+  </si>
+  <si>
+    <t>karthik1780900809419</t>
+  </si>
+  <si>
+    <t>meena1780900813501</t>
+  </si>
+  <si>
+    <t>sanjay1780900817436</t>
+  </si>
+  <si>
+    <t>anitha1780900821459</t>
+  </si>
+  <si>
+    <t>vikram1780900825055</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1133,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>53</v>
@@ -1114,7 +1144,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>53</v>
@@ -1125,7 +1155,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>53</v>
@@ -1136,7 +1166,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>53</v>
@@ -1147,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>53</v>
@@ -1158,7 +1188,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>53</v>
@@ -1169,7 +1199,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>53</v>
@@ -1180,7 +1210,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>53</v>
@@ -1191,7 +1221,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>53</v>
@@ -1202,7 +1232,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>53</v>

--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B97F59ED-6BFC-4A8F-975B-606C3A332F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84C53A09-25C0-4B8B-96B4-39ED02618F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="1" r:id="rId1"/>
-    <sheet name="RegisteredUsers" sheetId="2" r:id="rId2"/>
+    <sheet name="BillPay" sheetId="3" r:id="rId2"/>
+    <sheet name="RegisteredUsers" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
   <si>
     <t>FirstName</t>
   </si>
@@ -190,10 +191,25 @@
     <t>vikram</t>
   </si>
   <si>
+    <t>PayeeName</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>AccountNumber</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>1/19, Anna Nagar</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>surya1780724649628</t>
+    <t>surya1781087003532</t>
   </si>
   <si>
     <t>1.2345678E7</t>
@@ -202,188 +218,37 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>arun1780724653144</t>
-  </si>
-  <si>
-    <t>priya1780724656497</t>
-  </si>
-  <si>
-    <t>rahul1780724660207</t>
-  </si>
-  <si>
-    <t>divya1780724663713</t>
-  </si>
-  <si>
-    <t>karthik1780724667406</t>
-  </si>
-  <si>
-    <t>meena1780724671492</t>
-  </si>
-  <si>
-    <t>sanjay1780724674846</t>
-  </si>
-  <si>
-    <t>anitha1780724678232</t>
-  </si>
-  <si>
-    <t>vikram1780724681625</t>
-  </si>
-  <si>
-    <t>surya1780724789995</t>
-  </si>
-  <si>
-    <t>arun1780724793559</t>
-  </si>
-  <si>
-    <t>priya1780724797024</t>
-  </si>
-  <si>
-    <t>rahul1780724800475</t>
-  </si>
-  <si>
-    <t>divya1780724803978</t>
-  </si>
-  <si>
-    <t>karthik1780724807490</t>
-  </si>
-  <si>
-    <t>meena1780724810975</t>
-  </si>
-  <si>
-    <t>sanjay1780724814560</t>
-  </si>
-  <si>
-    <t>anitha1780724818247</t>
-  </si>
-  <si>
-    <t>vikram1780724821740</t>
-  </si>
-  <si>
-    <t>surya1780725239875</t>
-  </si>
-  <si>
-    <t>arun1780725243485</t>
-  </si>
-  <si>
-    <t>priya1780725247314</t>
-  </si>
-  <si>
-    <t>rahul1780725251388</t>
-  </si>
-  <si>
-    <t>divya1780725255599</t>
-  </si>
-  <si>
-    <t>karthik1780725259504</t>
-  </si>
-  <si>
-    <t>meena1780725263659</t>
-  </si>
-  <si>
-    <t>sanjay1780725267591</t>
-  </si>
-  <si>
-    <t>anitha1780725271051</t>
-  </si>
-  <si>
-    <t>vikram1780725274948</t>
-  </si>
-  <si>
-    <t>surya1780743100276</t>
-  </si>
-  <si>
-    <t>arun1780743103686</t>
-  </si>
-  <si>
-    <t>priya1780743107074</t>
-  </si>
-  <si>
-    <t>rahul1780743110366</t>
-  </si>
-  <si>
-    <t>divya1780743113974</t>
-  </si>
-  <si>
-    <t>karthik1780743117322</t>
-  </si>
-  <si>
-    <t>meena1780743121643</t>
-  </si>
-  <si>
-    <t>sanjay1780743125435</t>
-  </si>
-  <si>
-    <t>anitha1780743129303</t>
-  </si>
-  <si>
-    <t>vikram1780743133676</t>
-  </si>
-  <si>
-    <t>surya1780744850810</t>
-  </si>
-  <si>
-    <t>arun1780744855452</t>
-  </si>
-  <si>
-    <t>priya1780744860025</t>
-  </si>
-  <si>
-    <t>rahul1780744864019</t>
-  </si>
-  <si>
-    <t>divya1780744868072</t>
-  </si>
-  <si>
-    <t>karthik1780744873319</t>
-  </si>
-  <si>
-    <t>meena1780744877513</t>
-  </si>
-  <si>
-    <t>sanjay1780744881493</t>
-  </si>
-  <si>
-    <t>anitha1780744886133</t>
-  </si>
-  <si>
-    <t>vikram1780744890699</t>
-  </si>
-  <si>
-    <t>surya1780900788437</t>
-  </si>
-  <si>
-    <t>arun1780900792094</t>
-  </si>
-  <si>
-    <t>priya1780900795925</t>
-  </si>
-  <si>
-    <t>rahul1780900800143</t>
-  </si>
-  <si>
-    <t>divya1780900804784</t>
-  </si>
-  <si>
-    <t>karthik1780900809419</t>
-  </si>
-  <si>
-    <t>meena1780900813501</t>
-  </si>
-  <si>
-    <t>sanjay1780900817436</t>
-  </si>
-  <si>
-    <t>anitha1780900821459</t>
-  </si>
-  <si>
-    <t>vikram1780900825055</t>
+    <t>arun1781087014824</t>
+  </si>
+  <si>
+    <t>priya1781087019988</t>
+  </si>
+  <si>
+    <t>rahul1781087025400</t>
+  </si>
+  <si>
+    <t>divya1781087032558</t>
+  </si>
+  <si>
+    <t>karthik1781087041666</t>
+  </si>
+  <si>
+    <t>meena1781087047485</t>
+  </si>
+  <si>
+    <t>sanjay1781087052829</t>
+  </si>
+  <si>
+    <t>anitha1781087057554</t>
+  </si>
+  <si>
+    <t>vikram1781087062945</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -421,10 +286,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,15 +606,15 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="10.0"/>
-    <col min="2" max="2" customWidth="true" width="9.85546875"/>
-    <col min="3" max="3" customWidth="true" width="12.85546875"/>
-    <col min="4" max="4" customWidth="true" width="10.7109375"/>
-    <col min="5" max="5" customWidth="true" width="10.5703125"/>
-    <col min="6" max="6" customWidth="true" width="9.85546875"/>
-    <col min="7" max="7" customWidth="true" width="11.7109375"/>
-    <col min="8" max="8" customWidth="true" width="13.42578125"/>
-    <col min="10" max="10" customWidth="true" width="9.42578125"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -786,322 +650,322 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>641001</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2">
         <v>9876543210</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>123456789</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>12345678</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="0">
+      <c r="F3">
         <v>641012</v>
       </c>
-      <c r="G3" s="0">
+      <c r="G3">
         <v>9876543211</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>123456780</v>
       </c>
-      <c r="I3" t="s" s="0">
+      <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3">
         <v>12345678</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s" s="0">
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="0">
+      <c r="F4">
         <v>641002</v>
       </c>
-      <c r="G4" s="0">
+      <c r="G4">
         <v>9876543212</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>123456781</v>
       </c>
-      <c r="I4" t="s" s="0">
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4">
         <v>12345678</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s" s="0">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" t="s" s="0">
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="0">
+      <c r="F5">
         <v>641004</v>
       </c>
-      <c r="G5" s="0">
+      <c r="G5">
         <v>9876543213</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>123456782</v>
       </c>
-      <c r="I5" t="s" s="0">
+      <c r="I5" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5">
         <v>12345678</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s" s="0">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s" s="0">
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="0">
+      <c r="F6">
         <v>641011</v>
       </c>
-      <c r="G6" s="0">
+      <c r="G6">
         <v>9876543214</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
         <v>123456783</v>
       </c>
-      <c r="I6" t="s" s="0">
+      <c r="I6" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6">
         <v>12345678</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s" s="0">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="D7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="0">
+      <c r="F7">
         <v>641005</v>
       </c>
-      <c r="G7" s="0">
+      <c r="G7">
         <v>9876543215</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7">
         <v>123456784</v>
       </c>
-      <c r="I7" t="s" s="0">
+      <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7">
         <v>12345678</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s" s="0">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="E8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="0">
+      <c r="F8">
         <v>641018</v>
       </c>
-      <c r="G8" s="0">
+      <c r="G8">
         <v>9876543216</v>
       </c>
-      <c r="H8" s="0">
+      <c r="H8">
         <v>123456785</v>
       </c>
-      <c r="I8" t="s" s="0">
+      <c r="I8" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="0">
+      <c r="J8">
         <v>12345678</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s" s="0">
+      <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s" s="0">
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" t="s" s="0">
+      <c r="E9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="0">
+      <c r="F9">
         <v>641014</v>
       </c>
-      <c r="G9" s="0">
+      <c r="G9">
         <v>9876543217</v>
       </c>
-      <c r="H9" s="0">
+      <c r="H9">
         <v>123456786</v>
       </c>
-      <c r="I9" t="s" s="0">
+      <c r="I9" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="0">
+      <c r="J9">
         <v>12345678</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s" s="0">
+      <c r="A10" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="D10" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s" s="0">
+      <c r="E10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="0">
+      <c r="F10">
         <v>641015</v>
       </c>
-      <c r="G10" s="0">
+      <c r="G10">
         <v>9876543218</v>
       </c>
-      <c r="H10" s="0">
+      <c r="H10">
         <v>123456787</v>
       </c>
-      <c r="I10" t="s" s="0">
+      <c r="I10" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="0">
+      <c r="J10">
         <v>12345678</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s" s="0">
+      <c r="A11" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>48</v>
       </c>
-      <c r="C11" t="s" s="0">
+      <c r="C11" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s" s="0">
+      <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="E11" t="s" s="0">
+      <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="0">
+      <c r="F11">
         <v>641041</v>
       </c>
-      <c r="G11" s="0">
+      <c r="G11">
         <v>9876543219</v>
       </c>
-      <c r="H11" s="0">
+      <c r="H11">
         <v>123456788</v>
       </c>
-      <c r="I11" t="s" s="0">
+      <c r="I11" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="0">
+      <c r="J11">
         <v>12345678</v>
       </c>
     </row>
@@ -1111,134 +975,204 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C38400C-ACD2-4693-BB2C-06161B314F3C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>641001</v>
+      </c>
+      <c r="F2">
+        <v>9876543210</v>
+      </c>
+      <c r="G2">
+        <v>12345</v>
+      </c>
+      <c r="H2">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{973C8F62-7DAF-4A32-AD23-037BB3CD50E7}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="12.5703125"/>
-    <col min="2" max="2" customWidth="true" width="12.0"/>
-    <col min="3" max="3" customWidth="true" width="12.28515625"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>111</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
-        <v>113</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>54</v>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
   <si>
     <t>FirstName</t>
   </si>
@@ -243,12 +243,103 @@
   </si>
   <si>
     <t>vikram1781087062945</t>
+  </si>
+  <si>
+    <t>surya1781163746143</t>
+  </si>
+  <si>
+    <t>arun1781163754766</t>
+  </si>
+  <si>
+    <t>priya1781163762207</t>
+  </si>
+  <si>
+    <t>rahul1781163769559</t>
+  </si>
+  <si>
+    <t>divya1781163778742</t>
+  </si>
+  <si>
+    <t>karthik1781163788158</t>
+  </si>
+  <si>
+    <t>meena1781163795156</t>
+  </si>
+  <si>
+    <t>sanjay1781163805087</t>
+  </si>
+  <si>
+    <t>anitha1781163816010</t>
+  </si>
+  <si>
+    <t>vikram1781163826221</t>
+  </si>
+  <si>
+    <t>surya1781164077142</t>
+  </si>
+  <si>
+    <t>arun1781164084932</t>
+  </si>
+  <si>
+    <t>priya1781164091677</t>
+  </si>
+  <si>
+    <t>rahul1781164099802</t>
+  </si>
+  <si>
+    <t>divya1781164115166</t>
+  </si>
+  <si>
+    <t>karthik1781164126096</t>
+  </si>
+  <si>
+    <t>meena1781164134123</t>
+  </si>
+  <si>
+    <t>sanjay1781164143590</t>
+  </si>
+  <si>
+    <t>anitha1781164151784</t>
+  </si>
+  <si>
+    <t>vikram1781164159502</t>
+  </si>
+  <si>
+    <t>surya1781170876594</t>
+  </si>
+  <si>
+    <t>arun1781170886222</t>
+  </si>
+  <si>
+    <t>priya1781170895266</t>
+  </si>
+  <si>
+    <t>rahul1781170902619</t>
+  </si>
+  <si>
+    <t>divya1781170907782</t>
+  </si>
+  <si>
+    <t>karthik1781170921696</t>
+  </si>
+  <si>
+    <t>meena1781170929878</t>
+  </si>
+  <si>
+    <t>sanjay1781170936914</t>
+  </si>
+  <si>
+    <t>anitha1781170945025</t>
+  </si>
+  <si>
+    <t>vikram1781170951463</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -606,15 +697,15 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="10.0"/>
+    <col min="2" max="2" customWidth="true" width="9.85546875"/>
+    <col min="3" max="3" customWidth="true" width="12.85546875"/>
+    <col min="4" max="4" customWidth="true" width="10.7109375"/>
+    <col min="5" max="5" customWidth="true" width="10.5703125"/>
+    <col min="6" max="6" customWidth="true" width="9.85546875"/>
+    <col min="7" max="7" customWidth="true" width="11.7109375"/>
+    <col min="8" max="8" customWidth="true" width="13.42578125"/>
+    <col min="10" max="10" customWidth="true" width="9.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -650,322 +741,322 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>641001</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>9876543210</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>123456789</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>641012</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>9876543211</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>123456780</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>641002</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="0">
         <v>9876543212</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>123456781</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>641004</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="0">
         <v>9876543213</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>123456782</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>641011</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="0">
         <v>9876543214</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>123456783</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>641005</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="0">
         <v>9876543215</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>123456784</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>641018</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="0">
         <v>9876543216</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>123456785</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>641014</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="0">
         <v>9876543217</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="0">
         <v>123456786</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <v>641015</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="0">
         <v>9876543218</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="0">
         <v>123456787</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <v>12345678</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <v>641041</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="0">
         <v>9876543219</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="0">
         <v>123456788</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="0">
         <v>12345678</v>
       </c>
     </row>
@@ -979,12 +1070,12 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="11.42578125"/>
+    <col min="2" max="2" customWidth="true" width="15.5703125"/>
+    <col min="3" max="3" customWidth="true" width="11.5703125"/>
+    <col min="4" max="4" customWidth="true" width="11.7109375"/>
+    <col min="6" max="6" customWidth="true" width="13.28515625"/>
+    <col min="7" max="7" customWidth="true" width="15.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1014,28 +1105,28 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>641001</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>9876543210</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>12345</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>500</v>
       </c>
     </row>
@@ -1049,129 +1140,129 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.5703125"/>
+    <col min="2" max="2" customWidth="true" width="12.0"/>
+    <col min="3" max="3" customWidth="true" width="12.28515625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>59</v>
       </c>
     </row>

--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="149">
   <si>
     <t>FirstName</t>
   </si>
@@ -333,6 +333,156 @@
   </si>
   <si>
     <t>vikram1781170951463</t>
+  </si>
+  <si>
+    <t>surya1781171587971</t>
+  </si>
+  <si>
+    <t>arun1781171596513</t>
+  </si>
+  <si>
+    <t>priya1781171606486</t>
+  </si>
+  <si>
+    <t>rahul1781171614123</t>
+  </si>
+  <si>
+    <t>divya1781171622366</t>
+  </si>
+  <si>
+    <t>karthik1781171630306</t>
+  </si>
+  <si>
+    <t>meena1781171638539</t>
+  </si>
+  <si>
+    <t>sanjay1781171646416</t>
+  </si>
+  <si>
+    <t>anitha1781171659611</t>
+  </si>
+  <si>
+    <t>vikram1781171669135</t>
+  </si>
+  <si>
+    <t>surya1781281313483</t>
+  </si>
+  <si>
+    <t>arun1781281318563</t>
+  </si>
+  <si>
+    <t>priya1781281326428</t>
+  </si>
+  <si>
+    <t>rahul1781281334311</t>
+  </si>
+  <si>
+    <t>divya1781281339429</t>
+  </si>
+  <si>
+    <t>karthik1781281344961</t>
+  </si>
+  <si>
+    <t>meena1781281353059</t>
+  </si>
+  <si>
+    <t>sanjay1781281359893</t>
+  </si>
+  <si>
+    <t>anitha1781281368593</t>
+  </si>
+  <si>
+    <t>vikram1781281373698</t>
+  </si>
+  <si>
+    <t>surya1781281705562</t>
+  </si>
+  <si>
+    <t>arun1781281712757</t>
+  </si>
+  <si>
+    <t>priya1781281719228</t>
+  </si>
+  <si>
+    <t>rahul1781281725295</t>
+  </si>
+  <si>
+    <t>divya1781281731757</t>
+  </si>
+  <si>
+    <t>karthik1781281739553</t>
+  </si>
+  <si>
+    <t>meena1781281745459</t>
+  </si>
+  <si>
+    <t>sanjay1781281750187</t>
+  </si>
+  <si>
+    <t>anitha1781281756074</t>
+  </si>
+  <si>
+    <t>vikram1781281761877</t>
+  </si>
+  <si>
+    <t>surya1781316590446</t>
+  </si>
+  <si>
+    <t>arun1781316594439</t>
+  </si>
+  <si>
+    <t>priya1781316598423</t>
+  </si>
+  <si>
+    <t>rahul1781316602745</t>
+  </si>
+  <si>
+    <t>divya1781316607219</t>
+  </si>
+  <si>
+    <t>karthik1781316611189</t>
+  </si>
+  <si>
+    <t>meena1781316634639</t>
+  </si>
+  <si>
+    <t>sanjay1781316638742</t>
+  </si>
+  <si>
+    <t>anitha1781316642939</t>
+  </si>
+  <si>
+    <t>vikram1781316650551</t>
+  </si>
+  <si>
+    <t>surya1781319304053</t>
+  </si>
+  <si>
+    <t>arun1781319312474</t>
+  </si>
+  <si>
+    <t>priya1781319317724</t>
+  </si>
+  <si>
+    <t>rahul1781319323951</t>
+  </si>
+  <si>
+    <t>divya1781319328053</t>
+  </si>
+  <si>
+    <t>karthik1781319332985</t>
+  </si>
+  <si>
+    <t>meena1781319337547</t>
+  </si>
+  <si>
+    <t>sanjay1781319357904</t>
+  </si>
+  <si>
+    <t>anitha1781319362058</t>
+  </si>
+  <si>
+    <t>vikram1781319366132</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1308,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>58</v>
@@ -1169,7 +1319,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s" s="0">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>58</v>
@@ -1180,7 +1330,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s" s="0">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>58</v>
@@ -1191,7 +1341,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s" s="0">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>58</v>
@@ -1202,7 +1352,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s" s="0">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>58</v>
@@ -1213,7 +1363,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s" s="0">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>58</v>
@@ -1224,7 +1374,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s" s="0">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>58</v>
@@ -1235,7 +1385,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s" s="0">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>58</v>
@@ -1246,7 +1396,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s" s="0">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>58</v>
@@ -1257,7 +1407,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s" s="0">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>58</v>

--- a/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
+++ b/parabank-automation-framework/src/test/resources/TestData/TestData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="169">
   <si>
     <t>FirstName</t>
   </si>
@@ -483,6 +483,66 @@
   </si>
   <si>
     <t>vikram1781319366132</t>
+  </si>
+  <si>
+    <t>surya1781328212384</t>
+  </si>
+  <si>
+    <t>arun1781328216474</t>
+  </si>
+  <si>
+    <t>priya1781328220538</t>
+  </si>
+  <si>
+    <t>rahul1781328224662</t>
+  </si>
+  <si>
+    <t>divya1781328229248</t>
+  </si>
+  <si>
+    <t>karthik1781328233348</t>
+  </si>
+  <si>
+    <t>meena1781328237996</t>
+  </si>
+  <si>
+    <t>sanjay1781328242427</t>
+  </si>
+  <si>
+    <t>anitha1781328247195</t>
+  </si>
+  <si>
+    <t>vikram1781328251624</t>
+  </si>
+  <si>
+    <t>surya1781495391711</t>
+  </si>
+  <si>
+    <t>arun1781495395772</t>
+  </si>
+  <si>
+    <t>priya1781495400175</t>
+  </si>
+  <si>
+    <t>rahul1781495404476</t>
+  </si>
+  <si>
+    <t>divya1781495408630</t>
+  </si>
+  <si>
+    <t>karthik1781495412697</t>
+  </si>
+  <si>
+    <t>meena1781495417137</t>
+  </si>
+  <si>
+    <t>sanjay1781495423287</t>
+  </si>
+  <si>
+    <t>anitha1781495427609</t>
+  </si>
+  <si>
+    <t>vikram1781495432094</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1368,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s" s="0">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s" s="0">
         <v>58</v>
@@ -1319,7 +1379,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s" s="0">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>58</v>
@@ -1330,7 +1390,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s" s="0">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>58</v>
@@ -1341,7 +1401,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s" s="0">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>58</v>
@@ -1352,7 +1412,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s" s="0">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>58</v>
@@ -1363,7 +1423,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s" s="0">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>58</v>
@@ -1374,7 +1434,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s" s="0">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B8" t="s" s="0">
         <v>58</v>
@@ -1385,7 +1445,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s" s="0">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="B9" t="s" s="0">
         <v>58</v>
@@ -1396,7 +1456,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s" s="0">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>58</v>
@@ -1407,7 +1467,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s" s="0">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s" s="0">
         <v>58</v>
